--- a/excel/mull-trans/Raspored_Podravska-Moslavina_Zona61_2026.xlsx
+++ b/excel/mull-trans/Raspored_Podravska-Moslavina_Zona61_2026.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Po vrsti" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raspored'!$A$4:$H$57</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Po vrsti'!$A$1:$D$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raspored'!$A$4:$H$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Po vrsti'!$A$1:$D$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>IFERROR(1/(1/_xlfn.MINIFS(Raspored!$A$5:$A$57,Raspored!$D$5:$D$57,"x",Raspored!$A$5:$A$57,"&gt;="&amp;$B$3)),"nema više u 2026.")</f>
+        <f>IFERROR(1/(1/_xlfn.MINIFS(Raspored!$A$5:$A$40,Raspored!$D$5:$D$40,"x",Raspored!$A$5:$A$40,"&gt;="&amp;$B$3)),"nema više u 2026.")</f>
         <v/>
       </c>
       <c r="C6" s="7">
@@ -686,7 +686,7 @@
         <v/>
       </c>
       <c r="E6" s="7">
-        <f>COUNTIF(Raspored!$D$5:$D$57,"x")</f>
+        <f>COUNTIF(Raspored!$D$5:$D$40,"x")</f>
         <v/>
       </c>
     </row>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>IFERROR(1/(1/_xlfn.MINIFS(Raspored!$A$5:$A$57,Raspored!$E$5:$E$57,"x",Raspored!$A$5:$A$57,"&gt;="&amp;$B$3)),"nema više u 2026.")</f>
+        <f>IFERROR(1/(1/_xlfn.MINIFS(Raspored!$A$5:$A$40,Raspored!$E$5:$E$40,"x",Raspored!$A$5:$A$40,"&gt;="&amp;$B$3)),"nema više u 2026.")</f>
         <v/>
       </c>
       <c r="C7" s="7">
@@ -709,7 +709,7 @@
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>COUNTIF(Raspored!$E$5:$E$57,"x")</f>
+        <f>COUNTIF(Raspored!$E$5:$E$40,"x")</f>
         <v/>
       </c>
     </row>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>IFERROR(1/(1/_xlfn.MINIFS(Raspored!$A$5:$A$57,Raspored!$F$5:$F$57,"x",Raspored!$A$5:$A$57,"&gt;="&amp;$B$3)),"nema više u 2026.")</f>
+        <f>IFERROR(1/(1/_xlfn.MINIFS(Raspored!$A$5:$A$40,Raspored!$F$5:$F$40,"x",Raspored!$A$5:$A$40,"&gt;="&amp;$B$3)),"nema više u 2026.")</f>
         <v/>
       </c>
       <c r="C8" s="7">
@@ -732,7 +732,7 @@
         <v/>
       </c>
       <c r="E8" s="7">
-        <f>COUNTIF(Raspored!$F$5:$F$57,"x")</f>
+        <f>COUNTIF(Raspored!$F$5:$F$40,"x")</f>
         <v/>
       </c>
     </row>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B9" s="6">
-        <f>IFERROR(1/(1/_xlfn.MINIFS(Raspored!$A$5:$A$57,Raspored!$G$5:$G$57,"x",Raspored!$A$5:$A$57,"&gt;="&amp;$B$3)),"nema više u 2026.")</f>
+        <f>IFERROR(1/(1/_xlfn.MINIFS(Raspored!$A$5:$A$40,Raspored!$G$5:$G$40,"x",Raspored!$A$5:$A$40,"&gt;="&amp;$B$3)),"nema više u 2026.")</f>
         <v/>
       </c>
       <c r="C9" s="7">
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="E9" s="7">
-        <f>COUNTIF(Raspored!$G$5:$G$57,"x")</f>
+        <f>COUNTIF(Raspored!$G$5:$G$40,"x")</f>
         <v/>
       </c>
     </row>
@@ -800,19 +800,19 @@
         </is>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A13,Raspored!$D$5:$D$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A13,Raspored!$D$5:$D$40,"x")</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A13,Raspored!$E$5:$E$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A13,Raspored!$E$5:$E$40,"x")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A13,Raspored!$F$5:$F$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A13,Raspored!$F$5:$F$40,"x")</f>
         <v/>
       </c>
       <c r="E13" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A13,Raspored!$G$5:$G$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A13,Raspored!$G$5:$G$40,"x")</f>
         <v/>
       </c>
     </row>
@@ -823,19 +823,19 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A14,Raspored!$D$5:$D$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A14,Raspored!$D$5:$D$40,"x")</f>
         <v/>
       </c>
       <c r="C14" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A14,Raspored!$E$5:$E$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A14,Raspored!$E$5:$E$40,"x")</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A14,Raspored!$F$5:$F$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A14,Raspored!$F$5:$F$40,"x")</f>
         <v/>
       </c>
       <c r="E14" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A14,Raspored!$G$5:$G$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A14,Raspored!$G$5:$G$40,"x")</f>
         <v/>
       </c>
     </row>
@@ -846,19 +846,19 @@
         </is>
       </c>
       <c r="B15" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A15,Raspored!$D$5:$D$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A15,Raspored!$D$5:$D$40,"x")</f>
         <v/>
       </c>
       <c r="C15" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A15,Raspored!$E$5:$E$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A15,Raspored!$E$5:$E$40,"x")</f>
         <v/>
       </c>
       <c r="D15" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A15,Raspored!$F$5:$F$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A15,Raspored!$F$5:$F$40,"x")</f>
         <v/>
       </c>
       <c r="E15" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A15,Raspored!$G$5:$G$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A15,Raspored!$G$5:$G$40,"x")</f>
         <v/>
       </c>
     </row>
@@ -869,19 +869,19 @@
         </is>
       </c>
       <c r="B16" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A16,Raspored!$D$5:$D$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A16,Raspored!$D$5:$D$40,"x")</f>
         <v/>
       </c>
       <c r="C16" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A16,Raspored!$E$5:$E$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A16,Raspored!$E$5:$E$40,"x")</f>
         <v/>
       </c>
       <c r="D16" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A16,Raspored!$F$5:$F$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A16,Raspored!$F$5:$F$40,"x")</f>
         <v/>
       </c>
       <c r="E16" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A16,Raspored!$G$5:$G$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A16,Raspored!$G$5:$G$40,"x")</f>
         <v/>
       </c>
     </row>
@@ -892,19 +892,19 @@
         </is>
       </c>
       <c r="B17" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A17,Raspored!$D$5:$D$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A17,Raspored!$D$5:$D$40,"x")</f>
         <v/>
       </c>
       <c r="C17" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A17,Raspored!$E$5:$E$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A17,Raspored!$E$5:$E$40,"x")</f>
         <v/>
       </c>
       <c r="D17" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A17,Raspored!$F$5:$F$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A17,Raspored!$F$5:$F$40,"x")</f>
         <v/>
       </c>
       <c r="E17" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A17,Raspored!$G$5:$G$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A17,Raspored!$G$5:$G$40,"x")</f>
         <v/>
       </c>
     </row>
@@ -915,19 +915,19 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A18,Raspored!$D$5:$D$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A18,Raspored!$D$5:$D$40,"x")</f>
         <v/>
       </c>
       <c r="C18" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A18,Raspored!$E$5:$E$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A18,Raspored!$E$5:$E$40,"x")</f>
         <v/>
       </c>
       <c r="D18" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A18,Raspored!$F$5:$F$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A18,Raspored!$F$5:$F$40,"x")</f>
         <v/>
       </c>
       <c r="E18" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A18,Raspored!$G$5:$G$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A18,Raspored!$G$5:$G$40,"x")</f>
         <v/>
       </c>
     </row>
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B19" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A19,Raspored!$D$5:$D$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A19,Raspored!$D$5:$D$40,"x")</f>
         <v/>
       </c>
       <c r="C19" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A19,Raspored!$E$5:$E$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A19,Raspored!$E$5:$E$40,"x")</f>
         <v/>
       </c>
       <c r="D19" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A19,Raspored!$F$5:$F$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A19,Raspored!$F$5:$F$40,"x")</f>
         <v/>
       </c>
       <c r="E19" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A19,Raspored!$G$5:$G$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A19,Raspored!$G$5:$G$40,"x")</f>
         <v/>
       </c>
     </row>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B20" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A20,Raspored!$D$5:$D$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A20,Raspored!$D$5:$D$40,"x")</f>
         <v/>
       </c>
       <c r="C20" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A20,Raspored!$E$5:$E$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A20,Raspored!$E$5:$E$40,"x")</f>
         <v/>
       </c>
       <c r="D20" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A20,Raspored!$F$5:$F$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A20,Raspored!$F$5:$F$40,"x")</f>
         <v/>
       </c>
       <c r="E20" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A20,Raspored!$G$5:$G$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A20,Raspored!$G$5:$G$40,"x")</f>
         <v/>
       </c>
     </row>
@@ -984,19 +984,19 @@
         </is>
       </c>
       <c r="B21" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A21,Raspored!$D$5:$D$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A21,Raspored!$D$5:$D$40,"x")</f>
         <v/>
       </c>
       <c r="C21" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A21,Raspored!$E$5:$E$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A21,Raspored!$E$5:$E$40,"x")</f>
         <v/>
       </c>
       <c r="D21" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A21,Raspored!$F$5:$F$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A21,Raspored!$F$5:$F$40,"x")</f>
         <v/>
       </c>
       <c r="E21" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A21,Raspored!$G$5:$G$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A21,Raspored!$G$5:$G$40,"x")</f>
         <v/>
       </c>
     </row>
@@ -1007,19 +1007,19 @@
         </is>
       </c>
       <c r="B22" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A22,Raspored!$D$5:$D$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A22,Raspored!$D$5:$D$40,"x")</f>
         <v/>
       </c>
       <c r="C22" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A22,Raspored!$E$5:$E$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A22,Raspored!$E$5:$E$40,"x")</f>
         <v/>
       </c>
       <c r="D22" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A22,Raspored!$F$5:$F$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A22,Raspored!$F$5:$F$40,"x")</f>
         <v/>
       </c>
       <c r="E22" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A22,Raspored!$G$5:$G$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A22,Raspored!$G$5:$G$40,"x")</f>
         <v/>
       </c>
     </row>
@@ -1030,19 +1030,19 @@
         </is>
       </c>
       <c r="B23" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A23,Raspored!$D$5:$D$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A23,Raspored!$D$5:$D$40,"x")</f>
         <v/>
       </c>
       <c r="C23" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A23,Raspored!$E$5:$E$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A23,Raspored!$E$5:$E$40,"x")</f>
         <v/>
       </c>
       <c r="D23" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A23,Raspored!$F$5:$F$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A23,Raspored!$F$5:$F$40,"x")</f>
         <v/>
       </c>
       <c r="E23" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A23,Raspored!$G$5:$G$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A23,Raspored!$G$5:$G$40,"x")</f>
         <v/>
       </c>
     </row>
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A24,Raspored!$D$5:$D$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A24,Raspored!$D$5:$D$40,"x")</f>
         <v/>
       </c>
       <c r="C24" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A24,Raspored!$E$5:$E$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A24,Raspored!$E$5:$E$40,"x")</f>
         <v/>
       </c>
       <c r="D24" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A24,Raspored!$F$5:$F$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A24,Raspored!$F$5:$F$40,"x")</f>
         <v/>
       </c>
       <c r="E24" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$57,$A24,Raspored!$G$5:$G$57,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$40,$A24,Raspored!$G$5:$G$40,"x")</f>
         <v/>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
     <row r="29">
       <c r="A29" s="21" t="inlineStr">
         <is>
-          <t>• Izvor: https://mull-trans.hr/wp-content/uploads/2026/04/OPCINA-PODRAVSKA-MOSLAVINA-raspored-odvoza-otpada-za-2026.pdf (PDF izmijenjen 20.04.2026.)</t>
+          <t>• Od 7.9.2026. odvoz obavlja Doroslov d.o.o.; ovdje je raspored do tada. Izvor: https://mull-trans.hr/wp-content/uploads/2026/04/OPCINA-PODRAVSKA-MOSLAVINA-raspored-odvoza-otpada-za-2026.pdf (PDF izmijenjen 20.04.2026.)</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2146,457 +2146,29 @@
       <c r="G40" s="7" t="n"/>
       <c r="H40" s="23" t="n"/>
     </row>
-    <row r="41">
-      <c r="A41" s="6" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>rujan</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="n"/>
-      <c r="F41" s="7" t="n"/>
-      <c r="G41" s="7" t="n"/>
-      <c r="H41" s="23" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>rujan</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="n"/>
-      <c r="F42" s="7" t="n"/>
-      <c r="G42" s="7" t="n"/>
-      <c r="H42" s="23" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>rujan</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="n"/>
-      <c r="F43" s="7" t="n"/>
-      <c r="G43" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="H43" s="23" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>rujan</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="n"/>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="n"/>
-      <c r="H44" s="23" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="n">
-        <v>46300</v>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>listopad</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="n"/>
-      <c r="F45" s="7" t="n"/>
-      <c r="G45" s="7" t="n"/>
-      <c r="H45" s="23" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="n">
-        <v>46307</v>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="inlineStr">
-        <is>
-          <t>listopad</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="n"/>
-      <c r="F46" s="7" t="n"/>
-      <c r="G46" s="7" t="n"/>
-      <c r="H46" s="23" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>listopad</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="n"/>
-      <c r="F47" s="7" t="n"/>
-      <c r="G47" s="7" t="n"/>
-      <c r="H47" s="23" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="n">
-        <v>46322</v>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>listopad</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="n"/>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="n"/>
-      <c r="H48" s="23" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="n">
-        <v>46328</v>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>studeni</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="n"/>
-      <c r="F49" s="7" t="n"/>
-      <c r="G49" s="7" t="n"/>
-      <c r="H49" s="23" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="n">
-        <v>46335</v>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>studeni</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="n"/>
-      <c r="G50" s="7" t="n"/>
-      <c r="H50" s="23" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="n">
-        <v>46342</v>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>studeni</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="n"/>
-      <c r="G51" s="7" t="n"/>
-      <c r="H51" s="23" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="n">
-        <v>46349</v>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>studeni</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="n"/>
-      <c r="F52" s="7" t="n"/>
-      <c r="G52" s="7" t="n"/>
-      <c r="H52" s="23" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="n">
-        <v>46350</v>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>studeni</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="n"/>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="n"/>
-      <c r="H53" s="23" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="n">
-        <v>46363</v>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>prosinac</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="n"/>
-      <c r="G54" s="7" t="n"/>
-      <c r="H54" s="23" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="n">
-        <v>46370</v>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>prosinac</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="n"/>
-      <c r="G55" s="7" t="n"/>
-      <c r="H55" s="23" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="n">
-        <v>46377</v>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>prosinac</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="n"/>
-      <c r="F56" s="7" t="n"/>
-      <c r="G56" s="7" t="n"/>
-      <c r="H56" s="23" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="n">
-        <v>46385</v>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>prosinac</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="n"/>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="n"/>
-      <c r="H57" s="23" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:H57"/>
-  <conditionalFormatting sqref="D5:D57">
+  <autoFilter ref="A4:H40"/>
+  <conditionalFormatting sqref="D5:D40">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>D5="x"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E57">
+  <conditionalFormatting sqref="E5:E40">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>E5="x"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F57">
+  <conditionalFormatting sqref="F5:F40">
     <cfRule type="expression" priority="3" dxfId="2">
       <formula>F5="x"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G57">
+  <conditionalFormatting sqref="G5:G40">
     <cfRule type="expression" priority="4" dxfId="3">
       <formula>G5="x"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:H57">
+  <conditionalFormatting sqref="A5:H40">
     <cfRule type="expression" priority="5" dxfId="4" stopIfTrue="0">
       <formula>$A5&lt;TODAY()</formula>
     </cfRule>
@@ -2611,7 +2183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3354,360 +2926,8 @@
       </c>
       <c r="D45" s="17" t="n"/>
     </row>
-    <row r="46">
-      <c r="A46" s="26" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B46" s="17" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>Miješani komunalni otpad</t>
-        </is>
-      </c>
-      <c r="D46" s="17" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="26" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B47" s="17" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>Miješani komunalni otpad</t>
-        </is>
-      </c>
-      <c r="D47" s="17" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="26" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B48" s="17" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>Miješani komunalni otpad</t>
-        </is>
-      </c>
-      <c r="D48" s="17" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="26" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B49" s="17" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>Glomazni otpad</t>
-        </is>
-      </c>
-      <c r="D49" s="17" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="26" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B50" s="17" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>Plastika i metal</t>
-        </is>
-      </c>
-      <c r="D50" s="17" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="26" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B51" s="17" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C51" s="10" t="inlineStr">
-        <is>
-          <t>Papir i karton</t>
-        </is>
-      </c>
-      <c r="D51" s="17" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="26" t="n">
-        <v>46300</v>
-      </c>
-      <c r="B52" s="17" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>Miješani komunalni otpad</t>
-        </is>
-      </c>
-      <c r="D52" s="17" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="26" t="n">
-        <v>46307</v>
-      </c>
-      <c r="B53" s="17" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>Miješani komunalni otpad</t>
-        </is>
-      </c>
-      <c r="D53" s="17" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="26" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B54" s="17" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>Miješani komunalni otpad</t>
-        </is>
-      </c>
-      <c r="D54" s="17" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="26" t="n">
-        <v>46322</v>
-      </c>
-      <c r="B55" s="17" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>Plastika i metal</t>
-        </is>
-      </c>
-      <c r="D55" s="17" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="26" t="n">
-        <v>46322</v>
-      </c>
-      <c r="B56" s="17" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C56" s="10" t="inlineStr">
-        <is>
-          <t>Papir i karton</t>
-        </is>
-      </c>
-      <c r="D56" s="17" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="26" t="n">
-        <v>46328</v>
-      </c>
-      <c r="B57" s="17" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>Miješani komunalni otpad</t>
-        </is>
-      </c>
-      <c r="D57" s="17" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="26" t="n">
-        <v>46335</v>
-      </c>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>Miješani komunalni otpad</t>
-        </is>
-      </c>
-      <c r="D58" s="17" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="26" t="n">
-        <v>46342</v>
-      </c>
-      <c r="B59" s="17" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>Miješani komunalni otpad</t>
-        </is>
-      </c>
-      <c r="D59" s="17" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="26" t="n">
-        <v>46349</v>
-      </c>
-      <c r="B60" s="17" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>Miješani komunalni otpad</t>
-        </is>
-      </c>
-      <c r="D60" s="17" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="26" t="n">
-        <v>46350</v>
-      </c>
-      <c r="B61" s="17" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C61" s="9" t="inlineStr">
-        <is>
-          <t>Plastika i metal</t>
-        </is>
-      </c>
-      <c r="D61" s="17" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="26" t="n">
-        <v>46350</v>
-      </c>
-      <c r="B62" s="17" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C62" s="10" t="inlineStr">
-        <is>
-          <t>Papir i karton</t>
-        </is>
-      </c>
-      <c r="D62" s="17" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="26" t="n">
-        <v>46363</v>
-      </c>
-      <c r="B63" s="17" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>Miješani komunalni otpad</t>
-        </is>
-      </c>
-      <c r="D63" s="17" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="26" t="n">
-        <v>46370</v>
-      </c>
-      <c r="B64" s="17" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>Miješani komunalni otpad</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="26" t="n">
-        <v>46377</v>
-      </c>
-      <c r="B65" s="17" t="inlineStr">
-        <is>
-          <t>ponedjeljak</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>Miješani komunalni otpad</t>
-        </is>
-      </c>
-      <c r="D65" s="17" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="26" t="n">
-        <v>46385</v>
-      </c>
-      <c r="B66" s="17" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C66" s="9" t="inlineStr">
-        <is>
-          <t>Plastika i metal</t>
-        </is>
-      </c>
-      <c r="D66" s="17" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="26" t="n">
-        <v>46385</v>
-      </c>
-      <c r="B67" s="17" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C67" s="10" t="inlineStr">
-        <is>
-          <t>Papir i karton</t>
-        </is>
-      </c>
-      <c r="D67" s="17" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D67"/>
+  <autoFilter ref="A1:D45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>